--- a/docs/architecture/mau.xlsx
+++ b/docs/architecture/mau.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8400"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Trang_tính1" sheetId="1" r:id="rId1"/>
@@ -78,20 +78,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,154 +541,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1044,7 +1038,7 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="11.4444444444444"/>
+    <col min="3" max="3" width="11.4444444444444" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1054,7 +1048,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1075,7 +1069,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1095,7 +1089,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1115,7 +1109,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1135,7 +1129,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D5">
         <v>1</v>
